--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6257-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6257-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{226E680B-0B02-4734-8F39-A0C3F50B844B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{184AE7FF-B837-4375-9AB5-82C8175C69B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{AE184AF4-FD76-4B63-8E31-C68391846BBC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E386F729-DE55-4D2F-975A-5AF9CD9789B9}"/>
   </bookViews>
   <sheets>
     <sheet name="6257-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1448,21 +1448,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E0CC57-1AD9-435F-AB34-FB4E3AAB3D03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B405E8AD-4A67-4F02-8D11-0680EE598918}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2020</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>25</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2019</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2018</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2017</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2016</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2015</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2014</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2013</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2012</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2011</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2010</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2009</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2008</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2007</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2006</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2005</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2004</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2003</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2002</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2001</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39" t="s">
         <v>35</v>
       </c>
